--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137105913</v>
       </c>
       <c r="B3" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137105972</v>
       </c>
       <c r="B4" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137106007</v>
       </c>
       <c r="B6" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137106207</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137105913</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137105972</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137106007</v>
       </c>
       <c r="B6" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137106207</v>
       </c>
       <c r="B7" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137105913</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137105972</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137106329</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>137106007</v>
       </c>
       <c r="B6" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106207</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137105913</v>
       </c>
       <c r="B3" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>137105972</v>
       </c>
       <c r="B4" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>137106007</v>
       </c>
       <c r="B6" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106207</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,52 +791,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137105913</v>
+        <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>93492</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rockneby, Sm</t>
+          <t>Kåremo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579491</v>
+        <v>579362</v>
       </c>
       <c r="R3" t="n">
-        <v>6306150</v>
+        <v>6306005</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -863,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,16 +896,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105913</t>
+          <t>https://artportalen.se/Sighting/137373354</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137105972</v>
+        <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -943,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579454</v>
+        <v>579491</v>
       </c>
       <c r="R4" t="n">
-        <v>6306083</v>
+        <v>6306150</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1005,38 +1006,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105972</t>
+          <t>https://artportalen.se/Sighting/137105913</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137106329</v>
+        <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1044,9 +1045,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579399</v>
+        <v>579454</v>
       </c>
       <c r="R5" t="n">
-        <v>6305997</v>
+        <v>6306083</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1098,6 +1098,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,16 +1116,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106329</t>
+          <t>https://artportalen.se/Sighting/137105972</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137106007</v>
+        <v>137106329</v>
       </c>
       <c r="B6" t="n">
-        <v>106557</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,31 +1133,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579439</v>
+        <v>579399</v>
       </c>
       <c r="R6" t="n">
-        <v>6306059</v>
+        <v>6305997</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1208,7 +1209,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,16 +1226,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106007</t>
+          <t>https://artportalen.se/Sighting/137106329</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137106207</v>
+        <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>98267</v>
+        <v>106562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,26 +1243,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579404</v>
+        <v>579439</v>
       </c>
       <c r="R7" t="n">
-        <v>6306028</v>
+        <v>6306059</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1336,6 +1336,117 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137106207</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98272</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rockneby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579404</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6306028</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137106207</t>
         </is>
@@ -1349,6 +1460,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137106207</v>
       </c>
       <c r="B8" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137106329</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137106207</v>
       </c>
       <c r="B8" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137106207</v>
       </c>
       <c r="B8" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137106207</v>
       </c>
       <c r="B8" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137105913</v>
       </c>
       <c r="B4" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137105972</v>
       </c>
       <c r="B5" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137106007</v>
       </c>
       <c r="B7" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137106207</v>
       </c>
       <c r="B8" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2026 artfynd.xlsx
+++ b/artfynd/A 41136-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137106192</v>
       </c>
       <c r="B2" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137373354</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,55 +902,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137105913</v>
+        <v>137527991</v>
       </c>
       <c r="B4" t="n">
-        <v>93521</v>
+        <v>97023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rockneby, Sm</t>
+          <t>Dämsjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579491</v>
+        <v>579338</v>
       </c>
       <c r="R4" t="n">
-        <v>6306150</v>
+        <v>6306017</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,34 +990,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105913</t>
+          <t>https://artportalen.se/Sighting/137527991</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137105972</v>
+        <v>137105913</v>
       </c>
       <c r="B5" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579454</v>
+        <v>579491</v>
       </c>
       <c r="R5" t="n">
-        <v>6306083</v>
+        <v>6306150</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1116,38 +1117,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105972</t>
+          <t>https://artportalen.se/Sighting/137105913</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137106329</v>
+        <v>137105972</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>93525</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1155,9 +1156,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579399</v>
+        <v>579454</v>
       </c>
       <c r="R6" t="n">
-        <v>6305997</v>
+        <v>6306083</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1209,6 +1209,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,16 +1227,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106329</t>
+          <t>https://artportalen.se/Sighting/137105972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137106007</v>
+        <v>137106329</v>
       </c>
       <c r="B7" t="n">
-        <v>106588</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,31 +1244,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579439</v>
+        <v>579399</v>
       </c>
       <c r="R7" t="n">
-        <v>6306059</v>
+        <v>6305997</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1319,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,62 +1337,59 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106007</t>
+          <t>https://artportalen.se/Sighting/137106329</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137106207</v>
+        <v>137529159</v>
       </c>
       <c r="B8" t="n">
-        <v>98296</v>
+        <v>58199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rockneby, Sm</t>
+          <t>Dämsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579404</v>
+        <v>579332</v>
       </c>
       <c r="R8" t="n">
-        <v>6306028</v>
+        <v>6305987</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,12 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,23 +1427,662 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137529159</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137529259</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dämsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579377</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6305994</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137529259</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137530418</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dämsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579266</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6305997</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137530418</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137529565</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dämsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579266</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6305997</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137529565</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137531488</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111541</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dämsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6305943</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137531488</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137106007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106594</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rockneby, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579439</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6306059</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106007</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137106207</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rockneby, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579404</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6306028</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137106207</t>
         </is>
@@ -1461,6 +2097,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
